--- a/src/files/tempPDF/etatSalePaiemnt.xlsx
+++ b/src/files/tempPDF/etatSalePaiemnt.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Édité le : 26/02/2025 à 13:18:36
+    <t>Édité le : 02/03/2025 à 10:37:08
 Par : </t>
   </si>
   <si>
